--- a/teacher/tracker-core-pure.xlsx
+++ b/teacher/tracker-core-pure.xlsx
@@ -154,7 +154,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="6">
     <dxf>
       <font>
         <b val="1"/>
@@ -185,6 +185,42 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="001B998B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC0392B"/>
+          <bgColor rgb="FFC0392B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4A93F"/>
+          <bgColor rgb="FFF4A93F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF1B998B"/>
+          <bgColor rgb="FF1B998B"/>
         </patternFill>
       </fill>
     </dxf>
@@ -838,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1195,13 +1231,13 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:G27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1220,7 +1256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1547,13 +1583,13 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:F27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1572,7 +1608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1929,13 +1965,13 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:G27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1954,7 +1990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2251,13 +2287,13 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:E27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2276,7 +2312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2603,13 +2639,13 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:F27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2628,7 +2664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2925,13 +2961,13 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:E27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2950,7 +2986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3307,13 +3343,13 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:G27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3332,7 +3368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3719,13 +3755,13 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:H27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3744,7 +3780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4041,13 +4077,13 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:E27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
